--- a/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
+++ b/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
@@ -1282,13 +1282,13 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>孙国奉</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1902,15 +1902,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -1922,7 +1918,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1940,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2058,11 +2054,15 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2552,13 +2552,13 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -2594,13 +2594,13 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -2636,13 +2636,13 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -2678,15 +2678,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -2698,7 +2694,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2720,11 +2716,15 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2758,13 +2758,13 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -2842,15 +2842,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -2862,7 +2858,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2884,11 +2880,15 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2998,15 +2998,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -3018,7 +3014,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3036,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3078,11 +3074,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3450,11 +3450,15 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -3466,7 +3470,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3488,15 +3492,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -4408,14 +4408,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
@@ -4424,7 +4432,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4492,22 +4500,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4538,14 +4538,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
@@ -4554,7 +4562,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4576,22 +4584,14 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4622,20 +4622,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -4668,23 +4668,23 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -4718,22 +4718,26 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
@@ -4742,7 +4746,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4764,26 +4768,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4814,22 +4814,26 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -4838,7 +4842,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4860,20 +4864,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -4906,23 +4910,23 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>17952.0</t>
+          <t>408.0</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -4956,26 +4960,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5006,22 +5006,30 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -5030,7 +5038,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5052,20 +5060,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -5144,20 +5152,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
@@ -5190,22 +5198,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5214,7 +5230,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5236,30 +5252,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -5268,7 +5276,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5290,20 +5298,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -5336,27 +5344,27 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
           <t>360.0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>720.0</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -5390,20 +5398,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -5436,20 +5444,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -5482,20 +5490,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -5528,30 +5536,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5582,20 +5582,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -6606,11 +6606,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6630,7 +6626,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -6668,7 +6664,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -6706,7 +6702,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -6722,7 +6718,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6740,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -6758,7 +6754,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -7348,11 +7348,15 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -7362,11 +7366,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7386,15 +7386,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
@@ -7404,7 +7400,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -7576,7 +7576,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -7778,15 +7778,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
@@ -7798,7 +7794,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7820,7 +7816,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -7858,13 +7854,13 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G181" t="inlineStr"/>
@@ -7900,11 +7896,15 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7980,20 +7980,20 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
@@ -8068,20 +8068,20 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
@@ -8114,20 +8114,20 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
@@ -8202,20 +8202,20 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -8248,20 +8248,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J190" t="inlineStr"/>
@@ -8294,20 +8294,20 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="J191" t="inlineStr"/>
@@ -8735,7 +8735,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T10:04:41.147501</t>
+          <t>生成时间: 2026-06-12T14:44:15.914290</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
+++ b/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,10 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,6 +491,21 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>事件类型</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>增资后总股本(万股)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>认购占比</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>原文证据</t>
         </is>
       </c>
@@ -510,6 +528,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>设立</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>62.97%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>公司全称: 常州三协电机股份有限公司。证券代码: 920100。注册资本: 5,310.93万元。法定代表人: 盛祎。成立日期: 2002年11月7日。2002年11月至今，盛祎担任三协电机总经理，股份公司成立后担任董事长。</t>
         </is>
       </c>
@@ -532,6 +560,16 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>设立</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>19.49%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>公司全称: 常州三协电机股份有限公司。证券代码: 920100。注册资本: 5,310.93万元。法定代表人: 盛祎。成立日期: 2002年11月7日。2002年11月至今，盛祎担任三协电机总经理，股份公司成立后担任董事长。</t>
         </is>
       </c>
@@ -557,6 +595,16 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9.16%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>2022年6月24日，公司召开第二届董事会第四次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。本次股票发行价格为4.48元/股，共发行普通股530.00万股，募集资金总额为2,374.40万元，募集资金用途为补充流动资金。2022年8月15日，苏亚金诚出具《验资报告》（苏亚锡验[2022]7号），经审验，截至2022年8月9日，公司已收到稳正景明、长泽创投缴纳的出资款2,374.40万元。</t>
         </is>
       </c>
@@ -582,6 +630,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>2022年6月24日，公司召开第二届董事会第四次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。本次股票发行价格为4.48元/股，共发行普通股530.00万股，募集资金总额为2,374.40万元，募集资金用途为补充流动资金。2022年8月15日，苏亚金诚出具《验资报告》（苏亚锡验[2022]7号），经审验，截至2022年8月9日，公司已收到稳正景明、长泽创投缴纳的出资款2,374.40万元。</t>
         </is>
       </c>
@@ -612,6 +665,11 @@
         <v>5.41</v>
       </c>
       <c r="G6" t="inlineStr">
+        <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>2023年5月26日，公司召开第二届董事会第十三次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。本次股票拟发行价格为5.41元/股，拟发行普通股321.50万股，拟募集资金总额为1,739.32万元。2023年9月8日，苏亚金诚出具《验资报告》（苏亚验[2023]10号），经审验，截至2023年9月6日，公司已收到盛祎、盛松、薛小丽、倪进宽、余方成、吴春扣、陆宇君、戈翔俊、陈都亮、圣利、董雪强、文涛、付荷庆、陈韵和盛月瑶15名认购人缴纳的出资款1,723.09万元。</t>
         </is>
@@ -628,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -640,7 +698,10 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -691,6 +752,21 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>快照序号</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>股东类型</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>原始创始人</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>原文证据</t>
         </is>
       </c>
@@ -723,6 +799,21 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>公司全称: 常州三协电机股份有限公司。证券代码: 920100。注册资本: 5,310.93万元。法定代表人: 盛祎。成立日期: 2002年11月7日。2002年11月至今，盛祎担任三协电机总经理，股份公司成立后担任董事长。</t>
         </is>
       </c>
@@ -755,6 +846,21 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>公司全称: 常州三协电机股份有限公司。证券代码: 920100。注册资本: 5,310.93万元。法定代表人: 盛祎。成立日期: 2002年11月7日。2002年11月至今，盛祎担任三协电机总经理，股份公司成立后担任董事长。</t>
         </is>
       </c>
@@ -786,6 +892,21 @@
         </is>
       </c>
       <c r="J4" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>2022年6月24日，公司召开第二届董事会第四次会议审议通过了《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》。本次股票发行价格为4.48元/股，共发行普通股530.00万股，募集资金总额为2,374.40万元，募集资金用途为补充流动资金。2022年8月15日，苏亚金诚出具《验资报告》（苏亚锡验[2022]7号），经审验，截至2022年8月9日，公司已收到稳正景明、长泽创投缴纳的出资款2,374.40万元。</t>
         </is>
@@ -802,7 +923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -976,100 +1097,84 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>evidence_text</t>
+          <t>event_context</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>str(min=20)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>source_page</t>
+          <t>post_event_total_shares</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>snapshot_date</t>
+          <t>post_event_total_capital</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>str(YYYY-MM-DD)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>snapshot_type</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>total_shares</t>
+          <t>subscription_ratio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>float|null</t>
+          <t>str|null</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1077,20 +1182,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>total_capital</t>
+          <t>evidence_text</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>str(min=20)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1100,7 +1209,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>shareholder_name</t>
+          <t>source_page</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1122,15 +1231,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>shares_held</t>
+          <t>snapshot_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>str(YYYY-MM-DD)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1140,15 +1253,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>capital_contribution</t>
+          <t>snapshot_type</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1158,12 +1275,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>shareholding_ratio</t>
+          <t>total_shares</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>str|null</t>
+          <t>float|null</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1176,433 +1293,269 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>total_capital</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>shareholder_name</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>shares_held</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>capital_contribution</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>shareholding_ratio</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>str|null</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>snapshot_order</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>int|null</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>shareholder_type_detail</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>is_original_founder</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>yes/no/unknown</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>evidence_text</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>str(min=20)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Cross-Check 结果（相邻时点股本追踪 + 认缴存量对应）</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>上一时点</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>当前时点</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D32" s="1" t="inlineStr">
         <is>
           <t>股东名称</t>
         </is>
       </c>
-      <c r="E24" s="1" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
         <is>
           <t>上一时点持股数
 (万股)</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F32" s="1" t="inlineStr">
         <is>
           <t>上一时点出资额
 (万元注册资本)</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>本次认缴/变化
 (万股)</t>
         </is>
       </c>
-      <c r="H24" s="1" t="inlineStr">
+      <c r="H32" s="1" t="inlineStr">
         <is>
           <t>预期变更后
 持股数(万股)</t>
         </is>
       </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="I32" s="1" t="inlineStr">
         <is>
           <t>PDF披露
 持股数(万股)</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
+      <c r="J32" s="1" t="inlineStr">
         <is>
           <t>差额(万股)</t>
         </is>
       </c>
-      <c r="K24" s="1" t="inlineStr">
+      <c r="K32" s="1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="L24" s="1" t="inlineStr">
+      <c r="L32" s="1" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>175.0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>孙国敏</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>张松满</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>武汉力源信息技术股份有限公司</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>深圳市云汉电子有限公司</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>175.0</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -1612,35 +1565,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1650,35 +1603,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -1690,7 +1643,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -1702,17 +1655,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1740,21 +1693,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -1778,21 +1735,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -1804,7 +1765,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -1816,17 +1777,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1842,7 +1803,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -1854,17 +1815,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1892,17 +1853,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1918,7 +1879,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -1930,17 +1891,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1968,17 +1929,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1994,7 +1955,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2006,17 +1967,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2032,7 +1993,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2044,25 +2005,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2074,7 +2031,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2086,17 +2043,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2112,7 +2069,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2124,17 +2081,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2150,7 +2107,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2162,17 +2119,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2200,17 +2157,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2238,17 +2195,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2264,7 +2221,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2276,21 +2233,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -2302,7 +2263,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2314,17 +2275,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2352,17 +2313,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2390,17 +2351,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2416,7 +2377,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2389,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2466,17 +2427,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2492,7 +2453,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2475,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2530,7 +2491,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2542,25 +2503,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -2572,7 +2529,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2584,25 +2541,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -2626,25 +2579,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>1584.0</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -2656,7 +2605,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2617,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2706,25 +2655,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -2736,7 +2681,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2748,25 +2693,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -2778,7 +2719,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2790,25 +2731,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -2820,7 +2757,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2832,17 +2769,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2015-12-03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2858,7 +2795,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2870,25 +2807,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>2018-06-28</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>2020-05-28</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -2900,7 +2833,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2912,21 +2845,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>2018-06-28</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>2020-05-28</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -2938,33 +2875,37 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -2976,33 +2917,37 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>7412.0</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -3014,33 +2959,37 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -3052,35 +3001,35 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3101,26 +3050,30 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1584.0</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -3130,31 +3083,39 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -3164,27 +3125,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3198,27 +3163,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3234,7 +3203,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3215,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3272,7 +3241,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3284,17 +3253,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3322,17 +3291,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3360,21 +3329,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -3398,25 +3371,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -3426,11 +3395,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3440,25 +3405,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -3468,11 +3429,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3482,17 +3439,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3506,11 +3463,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3520,17 +3473,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3546,7 +3499,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3558,12 +3511,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3584,7 +3537,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3596,12 +3549,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3634,12 +3587,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3672,25 +3625,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
@@ -3700,7 +3649,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3710,21 +3663,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
           <t>2022-05-26</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1153.0</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -3736,49 +3693,37 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>6999.972</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>-0.028</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -3786,49 +3731,41 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>2999.988</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>-0.012</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -3836,49 +3773,37 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>1499.994</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>-0.006</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -3886,49 +3811,37 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -3936,49 +3849,37 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -3986,99 +3887,75 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>148.6667</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>5000.0031</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>0.0031</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>price×shares vs amount diff=0.0%</t>
-        </is>
-      </c>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>3000.0012</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>0.0012</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4086,49 +3963,37 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>2912.5034</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2912.5</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>0.0034</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4136,7 +4001,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4149,34 +4014,34 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2000.0019</t>
+          <t>6999.972</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>7000.0</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0019</t>
+          <t>-0.028</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -4199,34 +4064,34 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1747.5007</t>
+          <t>2999.988</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1747.5</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -4249,34 +4114,34 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>999.9993</t>
+          <t>1499.994</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-0.0007</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -4304,29 +4169,29 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>999.9993</t>
+          <t>10000.0027</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-0.0007</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -4354,29 +4219,29 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>339.999</t>
+          <t>10000.0027</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -4396,35 +4261,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>5000.0031</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr"/>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.0031</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4432,7 +4301,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -4442,35 +4311,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>3000.0012</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4478,7 +4351,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -4488,27 +4361,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2912.5034</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2912.5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.0034</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4516,7 +4401,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -4526,35 +4411,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2000.0019</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr"/>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>0.0019</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4562,7 +4451,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -4572,27 +4461,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1747.5007</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1747.5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4600,7 +4501,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -4610,35 +4511,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr"/>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4646,7 +4551,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -4656,39 +4561,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4696,7 +4601,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -4706,39 +4611,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+          <t>339.999</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4746,7 +4651,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -4758,30 +4663,30 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
@@ -4804,36 +4709,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -4842,7 +4743,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4854,32 +4755,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -4888,7 +4781,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4900,36 +4793,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D113" t="inlineStr">
         <is>
           <t>罗世兵</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>204.0</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -4938,7 +4827,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4950,32 +4839,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -4984,7 +4865,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4996,40 +4877,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -5038,7 +4911,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5050,32 +4923,36 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -5084,7 +4961,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5096,30 +4973,30 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
@@ -5142,32 +5019,36 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -5176,7 +5057,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5188,40 +5069,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5230,7 +5103,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5242,32 +5115,36 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -5276,7 +5153,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5288,30 +5165,30 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -5334,37 +5211,33 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -5398,20 +5271,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -5444,20 +5317,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -5490,20 +5363,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -5536,20 +5409,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -5582,20 +5455,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -5616,39 +5489,43 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5656,7 +5533,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5666,39 +5543,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5706,7 +5579,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5716,39 +5589,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5756,7 +5625,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5766,39 +5635,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>罗世兵 (认缴→存量)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5806,7 +5671,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5816,39 +5681,43 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5856,7 +5725,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5866,39 +5735,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5906,7 +5771,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5916,39 +5781,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5956,7 +5817,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5827,11 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
           <t>2022-12-19</t>
@@ -5974,31 +5839,31 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6006,7 +5871,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6019,29 +5884,29 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
+          <t>上海泽升贸易有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6069,29 +5934,29 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -6119,29 +5984,29 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -6169,29 +6034,29 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
+          <t>罗世兵 (认缴→存量)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -6219,29 +6084,29 @@
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -6269,29 +6134,29 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -6319,29 +6184,29 @@
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -6374,24 +6239,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -6424,24 +6289,24 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
+          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -6463,30 +6328,42 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K145" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6494,37 +6371,49 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K146" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6532,37 +6421,49 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6570,71 +6471,99 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K148" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6642,37 +6571,49 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6680,37 +6621,49 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6718,37 +6671,49 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6756,7 +6721,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6743,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -6816,7 +6781,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -6854,7 +6819,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -6870,7 +6835,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6857,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -6915,22 +6880,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -6944,31 +6909,27 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -6991,22 +6952,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7022,29 +6983,29 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -7060,29 +7021,29 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7098,29 +7059,29 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7143,22 +7104,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7181,22 +7142,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7234,7 +7195,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7262,17 +7223,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -7288,7 +7249,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7300,17 +7261,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -7326,7 +7287,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7338,25 +7299,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -7366,7 +7323,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7376,17 +7337,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -7402,7 +7363,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7414,17 +7375,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -7452,17 +7413,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -7478,7 +7439,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7490,17 +7451,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -7516,7 +7477,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7528,17 +7489,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -7566,21 +7527,25 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
           <t>2020-02-26</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -7590,51 +7555,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>盛祎等15名自然人</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>1739.315</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>1723.09</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>16.225</t>
-        </is>
-      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7642,29 +7591,29 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.9%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -7687,22 +7636,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -7718,29 +7667,29 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -7756,29 +7705,29 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -7794,29 +7743,29 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -7832,37 +7781,33 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
@@ -7881,30 +7826,26 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -7923,34 +7864,42 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>2016-12-14</t>
-        </is>
-      </c>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
+          <t>盛祎等15名自然人</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>321.5</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1739.315</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1723.09</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>16.225</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7958,44 +7907,36 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.9%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
@@ -8004,37 +7945,33 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
@@ -8053,37 +7990,29 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
@@ -8104,32 +8033,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
@@ -8138,7 +8063,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8150,23 +8075,23 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G188" t="inlineStr"/>
@@ -8192,32 +8117,24 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
@@ -8238,32 +8155,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
@@ -8284,32 +8193,28 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>牛威(罗永红代持)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
@@ -8318,7 +8223,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8340,22 +8245,18 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
@@ -8364,7 +8265,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8275,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C193" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8382,31 +8287,23 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司 (认缴→存量)</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8414,7 +8311,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8321,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C194" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8432,7 +8333,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>策星九天 (认缴→存量)</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -8442,21 +8343,13 @@
           <t>2345.0781</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
         <is>
           <t>2345.0781</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8464,7 +8357,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8367,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C195" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8482,31 +8379,23 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>幸福一期 (认缴→存量)</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8514,7 +8403,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8524,7 +8413,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C196" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8532,31 +8425,23 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>策星揽月 (认缴→存量)</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8564,7 +8449,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8459,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C197" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8582,31 +8471,23 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>幸福二期 (认缴→存量)</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8614,7 +8495,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8624,7 +8505,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C198" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8632,31 +8517,23 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>策星银河 (认缴→存量)</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8664,7 +8541,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8551,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C199" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8682,31 +8563,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星逐日 (认缴→存量)</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8714,35 +8583,431 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
           <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="3" t="inlineStr">
-        <is>
-          <t>认缴流量: 5 条</t>
-        </is>
-      </c>
-    </row>
     <row r="202">
-      <c r="A202" s="3" t="inlineStr">
-        <is>
-          <t>股权存量: 3 条</t>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>策星九天 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T14:44:15.914290</t>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>幸福一期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>策星揽月 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>幸福二期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>策星银河 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>策星逐日 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>认缴流量: 5 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>股权存量: 3 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-12T15:16:11.104566</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
+++ b/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
@@ -1585,7 +1585,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>孙国敏</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1603,11 +1603,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1627,7 +1623,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1645,7 +1641,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1665,11 +1665,15 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -1681,7 +1685,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -1703,15 +1707,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2167,15 +2167,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -2187,7 +2183,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2205,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2225,7 +2221,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2243,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2263,7 +2259,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2281,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2301,7 +2297,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2319,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2339,7 +2335,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2361,11 +2357,15 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2817,13 +2817,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -2859,13 +2859,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -2901,13 +2901,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2943,13 +2943,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2985,13 +2985,13 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -3065,13 +3065,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3145,15 +3145,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -3165,7 +3161,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3187,11 +3183,15 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3263,15 +3263,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -3283,7 +3279,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3305,11 +3301,15 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3673,15 +3673,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -3693,7 +3689,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3757,11 +3753,15 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1153.0</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3833,11 +3833,15 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
@@ -3847,11 +3851,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3947,15 +3947,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
@@ -3965,7 +3961,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4673,14 +4673,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -4689,7 +4697,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4711,20 +4719,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -4757,22 +4765,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4803,22 +4803,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -4827,7 +4819,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4849,20 +4841,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
@@ -4895,14 +4887,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4933,22 +4933,26 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -4957,7 +4961,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4979,23 +4983,23 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>408.0</t>
+          <t>17952.0</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -5029,26 +5033,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5079,26 +5079,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5107,7 +5103,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5129,22 +5125,26 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5175,26 +5175,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
@@ -5203,7 +5199,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5225,22 +5221,26 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5271,30 +5271,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -5303,7 +5295,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5471,22 +5463,30 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5517,30 +5517,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
@@ -5549,7 +5541,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5571,20 +5563,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -5617,20 +5609,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -5663,20 +5655,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -5709,20 +5701,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -5755,22 +5747,30 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5801,20 +5801,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -5847,20 +5847,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6819,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -7423,7 +7423,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -7575,11 +7575,15 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
@@ -7589,11 +7593,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7613,15 +7613,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -7631,7 +7627,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -7945,7 +7945,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8005,7 +8005,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -8127,11 +8127,15 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
@@ -8143,7 +8147,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8165,7 +8169,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -8203,15 +8207,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8245,20 +8245,20 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
@@ -8291,18 +8291,22 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
@@ -8311,7 +8315,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8333,20 +8337,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -8379,20 +8383,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
@@ -8425,22 +8429,18 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8471,20 +8471,20 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J197" t="inlineStr"/>
@@ -8517,20 +8517,20 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -8563,20 +8563,20 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -9000,7 +9000,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T16:09:12.774296</t>
+          <t>生成时间: 2026-06-12T16:30:01.209633</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
+++ b/outputs/week2_excel/920100_三协电机_三表抽取.xlsx
@@ -923,7 +923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L143"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1665,15 +1665,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -1685,7 +1681,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1703,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1745,11 +1741,15 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2281,15 +2281,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -2323,11 +2319,15 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2817,13 +2817,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -2859,15 +2859,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -2879,7 +2875,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2901,13 +2897,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2943,13 +2939,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2985,11 +2981,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3023,13 +3023,13 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3065,13 +3065,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3107,15 +3107,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -3127,7 +3123,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3149,11 +3145,15 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3263,11 +3263,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -3279,7 +3283,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3305,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3339,15 +3343,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3673,11 +3673,15 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -3689,7 +3693,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3711,15 +3715,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3753,13 +3753,13 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>10377.0</t>
+          <t>1153.0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -3795,11 +3795,15 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
@@ -3809,11 +3813,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -3909,15 +3909,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -3927,7 +3923,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -4008,30 +4008,42 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>6999.972</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>-0.028</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4039,37 +4051,49 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2999.988</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>-0.012</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4077,37 +4101,49 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1499.994</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>-0.006</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4115,37 +4151,49 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>10000.0027</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4153,37 +4201,49 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>10000.0027</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4191,37 +4251,49 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>5000.0031</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.0031</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4229,37 +4301,49 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>3000.0012</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4267,37 +4351,49 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2912.5034</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2912.5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.0034</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4305,37 +4401,49 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2000.0019</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>0.0019</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4343,75 +4451,99 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1747.5007</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1747.5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>price×shares vs amount diff=0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4419,37 +4551,49 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4457,37 +4601,49 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>339.999</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4495,29 +4651,29 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -4540,29 +4696,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -4571,36 +4735,44 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -4609,36 +4781,44 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -4654,22 +4834,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -4692,42 +4872,38 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>盛祎等15名自然人</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1739.315</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1723.09</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>16.225</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4735,36 +4911,44 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.9%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -4780,29 +4964,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
@@ -4811,35 +5003,47 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>朱绶青</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
@@ -4856,33 +5060,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -4891,35 +5099,47 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>牛威</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
@@ -4929,35 +5149,47 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>吴功友</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
@@ -4967,39 +5199,47 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
@@ -5016,33 +5256,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -5051,42 +5295,42 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -5104,33 +5348,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
@@ -5139,42 +5387,42 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -5192,37 +5440,45 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>策星揽月</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -5231,44 +5487,52 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>幸福一期</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
@@ -5277,42 +5541,42 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -5330,33 +5594,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
@@ -5365,42 +5633,42 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -5418,37 +5686,45 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
@@ -5457,49 +5733,45 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司 (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5507,49 +5779,45 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>策星九天 (认缴→存量)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5557,49 +5825,45 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>幸福一期 (认缴→存量)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5607,42 +5871,42 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>策星揽月 (认缴→存量)</t>
+          <t>上海泽升贸易有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -5664,35 +5928,35 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>幸福二期 (认缴→存量)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -5714,35 +5978,35 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>策星银河 (认缴→存量)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -5764,35 +6028,35 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>策星逐日 (认缴→存量)</t>
+          <t>罗世兵 (认缴→存量)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -5811,24 +6075,2932 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
     <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>认缴流量: 5 条</t>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>股权存量: 3 条</t>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T17:00:58.872192</t>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Cheer Rise Consultants Limited</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>史建伟</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>周乃鼎</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>黄学英/刘鸿雁</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>深圳中证投资有限责任公司</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>厦门富凯海创投资管理有限责任公司</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>盛祎等15名自然人</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>321.5</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1739.315</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1723.09</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>16.225</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>price×shares vs amount diff=0.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>盛祎</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>朱绶青</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>四方股份</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>吴功友(王金林代持)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>吴功友</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>牛威(罗永红代持)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>策星九天</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>幸福二期</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>策星逐日</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>吴功友</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>幸福一期</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>策星揽月</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>策星九天 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>幸福一期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>策星揽月 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>幸福二期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>策星银河 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>策星逐日 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>认缴流量: 5 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>股权存量: 3 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-12T17:05:42.751860</t>
         </is>
       </c>
     </row>
